--- a/data/trans_dic/P12_2_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P12_2_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que refirió mucha energía alguna vez o algunas veces</t>
+          <t>Población que refirió mucha energía alguna vez o algunas veces (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,62; 33,47</t>
+          <t>27,95; 34,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,57; 30,46</t>
+          <t>24,71; 30,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,81; 32,01</t>
+          <t>25,59; 32,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,48; 32,58</t>
+          <t>25,43; 32,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,81; 44,21</t>
+          <t>38,82; 44,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,87; 38,2</t>
+          <t>32,82; 38,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,82; 41,52</t>
+          <t>34,91; 41,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,87; 38,4</t>
+          <t>33,11; 38,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,85; 38,79</t>
+          <t>34,79; 38,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,22; 34,22</t>
+          <t>30,25; 34,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,97; 36,81</t>
+          <t>31,83; 36,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,74; 35,12</t>
+          <t>30,77; 35,09</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 15,66</t>
+          <t>12,39; 15,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 14,72</t>
+          <t>11,66; 14,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,44; 13,28</t>
+          <t>10,55; 13,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,85; 14,85</t>
+          <t>8,75; 14,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,15; 23,43</t>
+          <t>19,41; 23,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,02; 22,03</t>
+          <t>18,07; 22,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,81; 18,22</t>
+          <t>14,92; 18,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 20,32</t>
+          <t>13,11; 20,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,38; 18,93</t>
+          <t>16,15; 18,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 17,51</t>
+          <t>15,08; 17,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,05; 15,35</t>
+          <t>13,04; 15,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,36; 17,01</t>
+          <t>12,33; 17,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,28; 18,75</t>
+          <t>12,3; 18,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,21; 17,01</t>
+          <t>10,67; 17,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,26; 14,93</t>
+          <t>8,9; 14,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,33; 19,24</t>
+          <t>13,4; 19,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,57; 28,8</t>
+          <t>20,76; 28,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,46; 21,31</t>
+          <t>13,65; 20,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,52; 18,24</t>
+          <t>11,61; 17,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,4</t>
+          <t>16,1; 21,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,25; 22,38</t>
+          <t>17,29; 22,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 17,7</t>
+          <t>12,68; 17,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 15,51</t>
+          <t>11,02; 15,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,68; 19,72</t>
+          <t>15,39; 19,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,28; 21,04</t>
+          <t>18,2; 21,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,03; 18,73</t>
+          <t>15,95; 18,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,39; 16,88</t>
+          <t>14,44; 16,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 17,61</t>
+          <t>12,05; 17,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,97; 31,19</t>
+          <t>28,09; 31,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,0; 27,02</t>
+          <t>23,94; 27,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,9; 23,78</t>
+          <t>20,92; 23,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,51; 23,39</t>
+          <t>17,53; 23,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,52; 25,71</t>
+          <t>23,6; 25,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,5; 22,5</t>
+          <t>20,47; 22,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,01; 19,94</t>
+          <t>18,08; 20,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 20,14</t>
+          <t>16,07; 20,16</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que refirió mucha energía alguna vez o algunas veces</t>
+          <t>Población que refirió mucha energía alguna vez o algunas veces (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>284935; 345277</t>
+          <t>288351; 350962</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>239218; 296601</t>
+          <t>240563; 296170</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>194474; 241125</t>
+          <t>192769; 244251</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130970; 167441</t>
+          <t>130702; 166487</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>510394; 581368</t>
+          <t>510541; 583489</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>439464; 510740</t>
+          <t>438742; 513311</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>345591; 412115</t>
+          <t>346467; 411394</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>248030; 289743</t>
+          <t>249835; 290265</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>817769; 910268</t>
+          <t>816528; 913656</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>698271; 790595</t>
+          <t>698919; 790531</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>558091; 642722</t>
+          <t>555782; 636440</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>389898; 445443</t>
+          <t>390250; 445077</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>206782; 265229</t>
+          <t>209872; 266132</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>227676; 288936</t>
+          <t>228786; 289956</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>216528; 275317</t>
+          <t>218706; 276948</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>202648; 340042</t>
+          <t>200319; 340319</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>304029; 372045</t>
+          <t>308172; 369898</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>315922; 386123</t>
+          <t>316712; 386396</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>294002; 361640</t>
+          <t>296132; 363218</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>283296; 454482</t>
+          <t>293175; 456192</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>537344; 621000</t>
+          <t>529898; 620273</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>562633; 650502</t>
+          <t>560167; 650926</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>529551; 623059</t>
+          <t>529385; 621822</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>559352; 769979</t>
+          <t>558410; 778347</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>67703; 103393</t>
+          <t>67821; 102777</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49021; 81671</t>
+          <t>51253; 85970</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50639; 81637</t>
+          <t>48698; 78636</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86190; 124381</t>
+          <t>86678; 124150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>97993; 137215</t>
+          <t>98907; 137364</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61573; 97523</t>
+          <t>62436; 94518</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63125; 99948</t>
+          <t>63653; 98507</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>107720; 140989</t>
+          <t>106066; 142011</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>177283; 230009</t>
+          <t>177733; 227173</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119714; 165961</t>
+          <t>118935; 166966</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>122509; 169827</t>
+          <t>120669; 166194</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>204700; 257396</t>
+          <t>200904; 256068</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>598980; 689419</t>
+          <t>596418; 688815</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>547858; 639927</t>
+          <t>544875; 639693</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>485401; 569436</t>
+          <t>487029; 568887</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>417053; 607759</t>
+          <t>415679; 607899</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>945138; 1053966</t>
+          <t>949121; 1056738</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>851357; 958418</t>
+          <t>849301; 958926</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>736748; 838297</t>
+          <t>737636; 842186</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>602533; 853720</t>
+          <t>639746; 862656</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1565663; 1710947</t>
+          <t>1570526; 1711115</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1427487; 1566741</t>
+          <t>1425796; 1580275</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1242908; 1375832</t>
+          <t>1247345; 1380883</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1158968; 1430459</t>
+          <t>1141279; 1431933</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_2_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P12_2_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,95; 34,02</t>
+          <t>28,18; 34,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,71; 30,42</t>
+          <t>24,69; 30,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,59; 32,42</t>
+          <t>25,86; 32,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,43; 32,39</t>
+          <t>24,09; 31,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,82; 44,37</t>
+          <t>38,59; 44,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,82; 38,4</t>
+          <t>32,89; 38,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,91; 41,45</t>
+          <t>34,62; 41,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,11; 38,47</t>
+          <t>32,42; 37,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,79; 38,93</t>
+          <t>34,72; 38,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,25; 34,21</t>
+          <t>30,07; 34,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,83; 36,45</t>
+          <t>32,02; 36,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,77; 35,09</t>
+          <t>29,7; 34,17</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,39; 15,72</t>
+          <t>12,37; 15,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 14,77</t>
+          <t>11,77; 15,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,55; 13,36</t>
+          <t>10,36; 13,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,75; 14,86</t>
+          <t>12,83; 15,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,41; 23,3</t>
+          <t>19,21; 23,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,07; 22,04</t>
+          <t>18,04; 21,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,92; 18,3</t>
+          <t>14,93; 18,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,11; 20,39</t>
+          <t>19,02; 21,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,15; 18,9</t>
+          <t>16,21; 18,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,08; 17,52</t>
+          <t>15,2; 17,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,04; 15,32</t>
+          <t>13,06; 15,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,33; 17,19</t>
+          <t>16,29; 18,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,3; 18,64</t>
+          <t>12,24; 18,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,67; 17,9</t>
+          <t>10,23; 17,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 14,38</t>
+          <t>9,11; 14,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 19,2</t>
+          <t>13,85; 19,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,76; 28,83</t>
+          <t>20,68; 28,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,65; 20,66</t>
+          <t>13,53; 20,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,61; 17,97</t>
+          <t>11,87; 17,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,1; 21,55</t>
+          <t>17,43; 22,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,29; 22,1</t>
+          <t>17,39; 22,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 17,8</t>
+          <t>12,88; 17,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,02; 15,18</t>
+          <t>11,1; 15,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,39; 19,61</t>
+          <t>16,52; 20,4</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,2; 21,02</t>
+          <t>18,06; 20,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,95; 18,72</t>
+          <t>16,01; 18,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 16,86</t>
+          <t>14,32; 16,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 17,62</t>
+          <t>15,62; 18,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,09; 31,27</t>
+          <t>28,22; 31,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,94; 27,03</t>
+          <t>23,85; 26,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,92; 23,89</t>
+          <t>20,86; 23,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,53; 23,63</t>
+          <t>22,17; 24,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,6; 25,71</t>
+          <t>23,63; 25,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,47; 22,69</t>
+          <t>20,41; 22,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 20,01</t>
+          <t>18,12; 20,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,07; 20,16</t>
+          <t>19,45; 21,21</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147565</t>
+          <t>159426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>267971</t>
+          <t>286271</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>415536</t>
+          <t>445697</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>288351; 350962</t>
+          <t>290748; 353558</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>240563; 296170</t>
+          <t>240371; 300727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>192769; 244251</t>
+          <t>194838; 242186</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130702; 166487</t>
+          <t>139156; 179153</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>510541; 583489</t>
+          <t>507503; 582457</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>438742; 513311</t>
+          <t>439683; 512184</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>346467; 411394</t>
+          <t>343595; 409668</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>249835; 290265</t>
+          <t>266116; 307389</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>816528; 913656</t>
+          <t>814791; 907286</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>698919; 790531</t>
+          <t>694783; 794664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>555782; 636440</t>
+          <t>559124; 638409</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>390250; 445077</t>
+          <t>415405; 477898</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>290854</t>
+          <t>317962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>393762</t>
+          <t>443125</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>684617</t>
+          <t>761087</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>209872; 266132</t>
+          <t>209399; 266867</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>228786; 289956</t>
+          <t>230969; 295498</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>218706; 276948</t>
+          <t>214717; 274164</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>200319; 340319</t>
+          <t>286283; 352402</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>308172; 369898</t>
+          <t>305065; 373017</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>316712; 386396</t>
+          <t>316187; 384123</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>296132; 363218</t>
+          <t>296496; 364082</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>293175; 456192</t>
+          <t>412712; 475093</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>529898; 620273</t>
+          <t>531935; 618974</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>560167; 650926</t>
+          <t>564947; 657599</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>529385; 621822</t>
+          <t>530230; 620501</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>558410; 778347</t>
+          <t>716860; 810269</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105374</t>
+          <t>117567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>124032</t>
+          <t>146107</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>229406</t>
+          <t>263674</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>67821; 102777</t>
+          <t>67493; 102226</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51253; 85970</t>
+          <t>49125; 82981</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48698; 78636</t>
+          <t>49802; 81206</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86678; 124150</t>
+          <t>98558; 138388</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>98907; 137364</t>
+          <t>98535; 137640</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62436; 94518</t>
+          <t>61922; 95646</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63653; 98507</t>
+          <t>65052; 97822</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>106066; 142011</t>
+          <t>127810; 166403</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>177733; 227173</t>
+          <t>178751; 230068</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118935; 166966</t>
+          <t>120753; 168521</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120669; 166194</t>
+          <t>121495; 166337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>200904; 256068</t>
+          <t>238767; 294798</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>543793</t>
+          <t>594955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>785765</t>
+          <t>875503</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1329559</t>
+          <t>1470458</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>596418; 688815</t>
+          <t>591793; 681939</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>544875; 639693</t>
+          <t>547000; 641924</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>487029; 568887</t>
+          <t>482958; 565377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>415679; 607899</t>
+          <t>549923; 642176</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>949121; 1056738</t>
+          <t>953571; 1057287</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>849301; 958926</t>
+          <t>846008; 956041</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>737636; 842186</t>
+          <t>735411; 836830</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>639746; 862656</t>
+          <t>825778; 918756</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1570526; 1711115</t>
+          <t>1573002; 1715364</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1425796; 1580275</t>
+          <t>1421648; 1565249</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1247345; 1380883</t>
+          <t>1250004; 1383323</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1141279; 1431933</t>
+          <t>1409059; 1536811</t>
         </is>
       </c>
     </row>
